--- a/labs/lab-06-build-an-interactive-workforce-and-attrition-dashboard/data/BrightPath_Workforce_Headcount.xlsx
+++ b/labs/lab-06-build-an-interactive-workforce-and-attrition-dashboard/data/BrightPath_Workforce_Headcount.xlsx
@@ -75,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -87,6 +87,9 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -795,7 +798,6 @@
       <c r="F2" s="4" t="n">
         <v>43473</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Active</t>
@@ -1204,7 +1206,6 @@
       <c r="F10" s="4" t="n">
         <v>43511</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Active</t>
@@ -1249,7 +1250,6 @@
       <c r="F11" s="4" t="n">
         <v>43512</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Active</t>
@@ -1294,7 +1294,6 @@
       <c r="F12" s="4" t="n">
         <v>43536</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Active</t>
@@ -1651,7 +1650,6 @@
       <c r="F19" s="4" t="n">
         <v>43573</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Active</t>
@@ -1904,7 +1902,6 @@
       <c r="F24" s="4" t="n">
         <v>43610</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Active</t>
@@ -2157,7 +2154,6 @@
       <c r="F29" s="4" t="n">
         <v>43646</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Active</t>
@@ -2202,7 +2198,6 @@
       <c r="F30" s="4" t="n">
         <v>43649</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Active</t>
@@ -2559,7 +2554,6 @@
       <c r="F37" s="4" t="n">
         <v>43715</v>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>Active</t>
@@ -2656,7 +2650,6 @@
       <c r="F39" s="4" t="n">
         <v>43749</v>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>Active</t>
@@ -2701,7 +2694,6 @@
       <c r="F40" s="4" t="n">
         <v>43752</v>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Active</t>
@@ -2850,7 +2842,6 @@
       <c r="F43" s="4" t="n">
         <v>43771</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>Active</t>
@@ -2895,7 +2886,6 @@
       <c r="F44" s="4" t="n">
         <v>43777</v>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Active</t>
@@ -3044,7 +3034,6 @@
       <c r="F47" s="4" t="n">
         <v>43807</v>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>Active</t>
@@ -3089,7 +3078,6 @@
       <c r="F48" s="4" t="n">
         <v>43807</v>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>Active</t>
@@ -3186,7 +3174,6 @@
       <c r="F50" s="4" t="n">
         <v>43812</v>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>Active</t>
@@ -3231,7 +3218,6 @@
       <c r="F51" s="4" t="n">
         <v>43814</v>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>Active</t>
@@ -3380,7 +3366,6 @@
       <c r="F54" s="4" t="n">
         <v>43839</v>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>Active</t>
@@ -3529,7 +3514,6 @@
       <c r="F57" s="4" t="n">
         <v>43875</v>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>Active</t>
@@ -3626,7 +3610,6 @@
       <c r="F59" s="4" t="n">
         <v>43893</v>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>Active</t>
@@ -4191,7 +4174,6 @@
       <c r="F70" s="4" t="n">
         <v>43955</v>
       </c>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>Active</t>
@@ -4444,7 +4426,6 @@
       <c r="F75" s="4" t="n">
         <v>43970</v>
       </c>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>Active</t>
@@ -4489,7 +4470,6 @@
       <c r="F76" s="4" t="n">
         <v>43975</v>
       </c>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>Active</t>
@@ -4638,7 +4618,6 @@
       <c r="F79" s="4" t="n">
         <v>43989</v>
       </c>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>Active</t>
@@ -4683,7 +4662,6 @@
       <c r="F80" s="4" t="n">
         <v>43992</v>
       </c>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>Active</t>
@@ -4780,7 +4758,6 @@
       <c r="F82" s="4" t="n">
         <v>43998</v>
       </c>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>Active</t>
@@ -4929,7 +4906,6 @@
       <c r="F85" s="4" t="n">
         <v>44018</v>
       </c>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>Active</t>
@@ -5026,7 +5002,6 @@
       <c r="F87" s="4" t="n">
         <v>44023</v>
       </c>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>Active</t>
@@ -5071,7 +5046,6 @@
       <c r="F88" s="4" t="n">
         <v>44029</v>
       </c>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>Active</t>
@@ -5116,7 +5090,6 @@
       <c r="F89" s="4" t="n">
         <v>44035</v>
       </c>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>Active</t>
@@ -5161,7 +5134,6 @@
       <c r="F90" s="4" t="n">
         <v>44036</v>
       </c>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>Active</t>
@@ -5258,7 +5230,6 @@
       <c r="F92" s="4" t="n">
         <v>44043</v>
       </c>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>Active</t>
@@ -5303,7 +5274,6 @@
       <c r="F93" s="4" t="n">
         <v>44057</v>
       </c>
-      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
           <t>Active</t>
@@ -5348,7 +5318,6 @@
       <c r="F94" s="4" t="n">
         <v>44058</v>
       </c>
-      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>Active</t>
@@ -5497,7 +5466,6 @@
       <c r="F97" s="4" t="n">
         <v>44079</v>
       </c>
-      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
           <t>Active</t>
@@ -5594,7 +5562,6 @@
       <c r="F99" s="4" t="n">
         <v>44090</v>
       </c>
-      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>Active</t>
@@ -5743,7 +5710,6 @@
       <c r="F102" s="4" t="n">
         <v>44095</v>
       </c>
-      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
           <t>Active</t>
@@ -5788,7 +5754,6 @@
       <c r="F103" s="4" t="n">
         <v>44098</v>
       </c>
-      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
           <t>Active</t>
@@ -5885,7 +5850,6 @@
       <c r="F105" s="4" t="n">
         <v>44114</v>
       </c>
-      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
           <t>Active</t>
@@ -5930,7 +5894,6 @@
       <c r="F106" s="4" t="n">
         <v>44120</v>
       </c>
-      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
           <t>Active</t>
@@ -6079,7 +6042,6 @@
       <c r="F109" s="4" t="n">
         <v>44124</v>
       </c>
-      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>Active</t>
@@ -6124,7 +6086,6 @@
       <c r="F110" s="4" t="n">
         <v>44134</v>
       </c>
-      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
           <t>Active</t>
@@ -6169,7 +6130,6 @@
       <c r="F111" s="4" t="n">
         <v>44136</v>
       </c>
-      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
           <t>Active</t>
@@ -6318,7 +6278,6 @@
       <c r="F114" s="4" t="n">
         <v>44148</v>
       </c>
-      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
           <t>Active</t>
@@ -6363,7 +6322,6 @@
       <c r="F115" s="4" t="n">
         <v>44153</v>
       </c>
-      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
           <t>Active</t>
@@ -6408,7 +6366,6 @@
       <c r="F116" s="4" t="n">
         <v>44153</v>
       </c>
-      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
           <t>Active</t>
@@ -6557,7 +6514,6 @@
       <c r="F119" s="4" t="n">
         <v>44156</v>
       </c>
-      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr">
         <is>
           <t>Active</t>
@@ -6602,7 +6558,6 @@
       <c r="F120" s="4" t="n">
         <v>44163</v>
       </c>
-      <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr">
         <is>
           <t>Active</t>
@@ -6959,7 +6914,6 @@
       <c r="F127" s="4" t="n">
         <v>44212</v>
       </c>
-      <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
           <t>Active</t>
@@ -7160,7 +7114,6 @@
       <c r="F131" s="4" t="n">
         <v>44233</v>
       </c>
-      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
           <t>Active</t>
@@ -7205,7 +7158,6 @@
       <c r="F132" s="4" t="n">
         <v>44236</v>
       </c>
-      <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
           <t>Active</t>
@@ -7302,7 +7254,6 @@
       <c r="F134" s="4" t="n">
         <v>44249</v>
       </c>
-      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
           <t>Active</t>
@@ -7347,7 +7298,6 @@
       <c r="F135" s="4" t="n">
         <v>44259</v>
       </c>
-      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
           <t>Active</t>
@@ -7392,7 +7342,6 @@
       <c r="F136" s="4" t="n">
         <v>44268</v>
       </c>
-      <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
           <t>Active</t>
@@ -7489,7 +7438,6 @@
       <c r="F138" s="4" t="n">
         <v>44288</v>
       </c>
-      <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr">
         <is>
           <t>Active</t>
@@ -7846,7 +7794,6 @@
       <c r="F145" s="4" t="n">
         <v>44311</v>
       </c>
-      <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr">
         <is>
           <t>Active</t>
@@ -8099,7 +8046,6 @@
       <c r="F150" s="4" t="n">
         <v>44337</v>
       </c>
-      <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr">
         <is>
           <t>Active</t>
@@ -8196,7 +8142,6 @@
       <c r="F152" s="4" t="n">
         <v>44350</v>
       </c>
-      <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr">
         <is>
           <t>Active</t>
@@ -8397,7 +8342,6 @@
       <c r="F156" s="4" t="n">
         <v>44359</v>
       </c>
-      <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr">
         <is>
           <t>Active</t>
@@ -8442,7 +8386,6 @@
       <c r="F157" s="4" t="n">
         <v>44371</v>
       </c>
-      <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr">
         <is>
           <t>Active</t>
@@ -8591,7 +8534,6 @@
       <c r="F160" s="4" t="n">
         <v>44391</v>
       </c>
-      <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr">
         <is>
           <t>Active</t>
@@ -8740,7 +8682,6 @@
       <c r="F163" s="4" t="n">
         <v>44422</v>
       </c>
-      <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr">
         <is>
           <t>Active</t>
@@ -8785,7 +8726,6 @@
       <c r="F164" s="4" t="n">
         <v>44430</v>
       </c>
-      <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr">
         <is>
           <t>Active</t>
@@ -8882,7 +8822,6 @@
       <c r="F166" s="4" t="n">
         <v>44458</v>
       </c>
-      <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr">
         <is>
           <t>Active</t>
@@ -8927,7 +8866,6 @@
       <c r="F167" s="4" t="n">
         <v>44464</v>
       </c>
-      <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr">
         <is>
           <t>Active</t>
@@ -9180,7 +9118,6 @@
       <c r="F172" s="4" t="n">
         <v>44478</v>
       </c>
-      <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr">
         <is>
           <t>Active</t>
@@ -9329,7 +9266,6 @@
       <c r="F175" s="4" t="n">
         <v>44510</v>
       </c>
-      <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr">
         <is>
           <t>Active</t>
@@ -9374,7 +9310,6 @@
       <c r="F176" s="4" t="n">
         <v>44546</v>
       </c>
-      <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr">
         <is>
           <t>Active</t>
@@ -9627,7 +9562,6 @@
       <c r="F181" s="4" t="n">
         <v>44568</v>
       </c>
-      <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr">
         <is>
           <t>Active</t>
@@ -9828,7 +9762,6 @@
       <c r="F185" s="4" t="n">
         <v>44598</v>
       </c>
-      <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr">
         <is>
           <t>Active</t>
@@ -9977,7 +9910,6 @@
       <c r="F188" s="4" t="n">
         <v>44611</v>
       </c>
-      <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr">
         <is>
           <t>Active</t>
@@ -10438,7 +10370,6 @@
       <c r="F197" s="4" t="n">
         <v>44689</v>
       </c>
-      <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
           <t>Active</t>
@@ -10483,7 +10414,6 @@
       <c r="F198" s="4" t="n">
         <v>44700</v>
       </c>
-      <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
           <t>Active</t>
@@ -10528,7 +10458,6 @@
       <c r="F199" s="4" t="n">
         <v>44702</v>
       </c>
-      <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
           <t>Active</t>
@@ -10573,7 +10502,6 @@
       <c r="F200" s="4" t="n">
         <v>44711</v>
       </c>
-      <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr">
         <is>
           <t>Active</t>
@@ -10618,7 +10546,6 @@
       <c r="F201" s="4" t="n">
         <v>44720</v>
       </c>
-      <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr">
         <is>
           <t>Active</t>
@@ -10663,7 +10590,6 @@
       <c r="F202" s="4" t="n">
         <v>44751</v>
       </c>
-      <c r="H202" t="inlineStr"/>
       <c r="I202" t="inlineStr">
         <is>
           <t>Active</t>
@@ -10708,7 +10634,6 @@
       <c r="F203" s="4" t="n">
         <v>44751</v>
       </c>
-      <c r="H203" t="inlineStr"/>
       <c r="I203" t="inlineStr">
         <is>
           <t>Active</t>
@@ -10805,7 +10730,6 @@
       <c r="F205" s="4" t="n">
         <v>44774</v>
       </c>
-      <c r="H205" t="inlineStr"/>
       <c r="I205" t="inlineStr">
         <is>
           <t>Active</t>
@@ -10902,7 +10826,6 @@
       <c r="F207" s="4" t="n">
         <v>44787</v>
       </c>
-      <c r="H207" t="inlineStr"/>
       <c r="I207" t="inlineStr">
         <is>
           <t>Active</t>
@@ -10999,7 +10922,6 @@
       <c r="F209" s="4" t="n">
         <v>44788</v>
       </c>
-      <c r="H209" t="inlineStr"/>
       <c r="I209" t="inlineStr">
         <is>
           <t>Active</t>
@@ -11044,7 +10966,6 @@
       <c r="F210" s="4" t="n">
         <v>44794</v>
       </c>
-      <c r="H210" t="inlineStr"/>
       <c r="I210" t="inlineStr">
         <is>
           <t>Active</t>
@@ -11297,7 +11218,6 @@
       <c r="F215" s="4" t="n">
         <v>44801</v>
       </c>
-      <c r="H215" t="inlineStr"/>
       <c r="I215" t="inlineStr">
         <is>
           <t>Active</t>
@@ -11342,7 +11262,6 @@
       <c r="F216" s="4" t="n">
         <v>44802</v>
       </c>
-      <c r="H216" t="inlineStr"/>
       <c r="I216" t="inlineStr">
         <is>
           <t>Active</t>
@@ -11387,7 +11306,6 @@
       <c r="F217" s="4" t="n">
         <v>44804</v>
       </c>
-      <c r="H217" t="inlineStr"/>
       <c r="I217" t="inlineStr">
         <is>
           <t>Active</t>
@@ -11432,7 +11350,6 @@
       <c r="F218" s="4" t="n">
         <v>44804</v>
       </c>
-      <c r="H218" t="inlineStr"/>
       <c r="I218" t="inlineStr">
         <is>
           <t>Active</t>
@@ -11477,7 +11394,6 @@
       <c r="F219" s="4" t="n">
         <v>44819</v>
       </c>
-      <c r="H219" t="inlineStr"/>
       <c r="I219" t="inlineStr">
         <is>
           <t>Active</t>
@@ -11522,7 +11438,6 @@
       <c r="F220" s="4" t="n">
         <v>44819</v>
       </c>
-      <c r="H220" t="inlineStr"/>
       <c r="I220" t="inlineStr">
         <is>
           <t>Active</t>
@@ -11567,7 +11482,6 @@
       <c r="F221" s="4" t="n">
         <v>44819</v>
       </c>
-      <c r="H221" t="inlineStr"/>
       <c r="I221" t="inlineStr">
         <is>
           <t>Active</t>
@@ -11664,7 +11578,6 @@
       <c r="F223" s="4" t="n">
         <v>44885</v>
       </c>
-      <c r="H223" t="inlineStr"/>
       <c r="I223" t="inlineStr">
         <is>
           <t>Active</t>
@@ -11709,7 +11622,6 @@
       <c r="F224" s="4" t="n">
         <v>44886</v>
       </c>
-      <c r="H224" t="inlineStr"/>
       <c r="I224" t="inlineStr">
         <is>
           <t>Active</t>
@@ -11858,7 +11770,6 @@
       <c r="F227" s="4" t="n">
         <v>44895</v>
       </c>
-      <c r="H227" t="inlineStr"/>
       <c r="I227" t="inlineStr">
         <is>
           <t>Active</t>
@@ -11955,7 +11866,6 @@
       <c r="F229" s="4" t="n">
         <v>44902</v>
       </c>
-      <c r="H229" t="inlineStr"/>
       <c r="I229" t="inlineStr">
         <is>
           <t>Active</t>
@@ -12000,7 +11910,6 @@
       <c r="F230" s="4" t="n">
         <v>44925</v>
       </c>
-      <c r="H230" t="inlineStr"/>
       <c r="I230" t="inlineStr">
         <is>
           <t>Active</t>
@@ -12201,7 +12110,6 @@
       <c r="F234" s="4" t="n">
         <v>44954</v>
       </c>
-      <c r="H234" t="inlineStr"/>
       <c r="I234" t="inlineStr">
         <is>
           <t>Active</t>
@@ -12246,7 +12154,6 @@
       <c r="F235" s="4" t="n">
         <v>44967</v>
       </c>
-      <c r="H235" t="inlineStr"/>
       <c r="I235" t="inlineStr">
         <is>
           <t>Active</t>
@@ -12291,7 +12198,6 @@
       <c r="F236" s="4" t="n">
         <v>44968</v>
       </c>
-      <c r="H236" t="inlineStr"/>
       <c r="I236" t="inlineStr">
         <is>
           <t>Active</t>
@@ -12336,7 +12242,6 @@
       <c r="F237" s="4" t="n">
         <v>44970</v>
       </c>
-      <c r="H237" t="inlineStr"/>
       <c r="I237" t="inlineStr">
         <is>
           <t>Active</t>
@@ -12381,7 +12286,6 @@
       <c r="F238" s="4" t="n">
         <v>44974</v>
       </c>
-      <c r="H238" t="inlineStr"/>
       <c r="I238" t="inlineStr">
         <is>
           <t>Active</t>
@@ -12426,7 +12330,6 @@
       <c r="F239" s="4" t="n">
         <v>44997</v>
       </c>
-      <c r="H239" t="inlineStr"/>
       <c r="I239" t="inlineStr">
         <is>
           <t>Active</t>
@@ -12471,7 +12374,6 @@
       <c r="F240" s="4" t="n">
         <v>45001</v>
       </c>
-      <c r="H240" t="inlineStr"/>
       <c r="I240" t="inlineStr">
         <is>
           <t>Active</t>
@@ -12568,7 +12470,6 @@
       <c r="F242" s="4" t="n">
         <v>45018</v>
       </c>
-      <c r="H242" t="inlineStr"/>
       <c r="I242" t="inlineStr">
         <is>
           <t>Active</t>
@@ -12717,7 +12618,6 @@
       <c r="F245" s="4" t="n">
         <v>45032</v>
       </c>
-      <c r="H245" t="inlineStr"/>
       <c r="I245" t="inlineStr">
         <is>
           <t>Active</t>
@@ -12866,7 +12766,6 @@
       <c r="F248" s="4" t="n">
         <v>45038</v>
       </c>
-      <c r="H248" t="inlineStr"/>
       <c r="I248" t="inlineStr">
         <is>
           <t>Active</t>
@@ -12911,7 +12810,6 @@
       <c r="F249" s="4" t="n">
         <v>45048</v>
       </c>
-      <c r="H249" t="inlineStr"/>
       <c r="I249" t="inlineStr">
         <is>
           <t>Active</t>
@@ -12956,7 +12854,6 @@
       <c r="F250" s="4" t="n">
         <v>45055</v>
       </c>
-      <c r="H250" t="inlineStr"/>
       <c r="I250" t="inlineStr">
         <is>
           <t>Active</t>
@@ -13157,7 +13054,6 @@
       <c r="F254" s="4" t="n">
         <v>45097</v>
       </c>
-      <c r="H254" t="inlineStr"/>
       <c r="I254" t="inlineStr">
         <is>
           <t>Active</t>
@@ -13254,7 +13150,6 @@
       <c r="F256" s="4" t="n">
         <v>45101</v>
       </c>
-      <c r="H256" t="inlineStr"/>
       <c r="I256" t="inlineStr">
         <is>
           <t>Active</t>
@@ -13299,7 +13194,6 @@
       <c r="F257" s="4" t="n">
         <v>45104</v>
       </c>
-      <c r="H257" t="inlineStr"/>
       <c r="I257" t="inlineStr">
         <is>
           <t>Active</t>
@@ -13344,7 +13238,6 @@
       <c r="F258" s="4" t="n">
         <v>45119</v>
       </c>
-      <c r="H258" t="inlineStr"/>
       <c r="I258" t="inlineStr">
         <is>
           <t>Active</t>
@@ -13545,7 +13438,6 @@
       <c r="F262" s="4" t="n">
         <v>45132</v>
       </c>
-      <c r="H262" t="inlineStr"/>
       <c r="I262" t="inlineStr">
         <is>
           <t>Active</t>
@@ -13642,7 +13534,6 @@
       <c r="F264" s="4" t="n">
         <v>45147</v>
       </c>
-      <c r="H264" t="inlineStr"/>
       <c r="I264" t="inlineStr">
         <is>
           <t>Active</t>
@@ -13687,7 +13578,6 @@
       <c r="F265" s="4" t="n">
         <v>45174</v>
       </c>
-      <c r="H265" t="inlineStr"/>
       <c r="I265" t="inlineStr">
         <is>
           <t>Active</t>
@@ -13732,7 +13622,6 @@
       <c r="F266" s="4" t="n">
         <v>45183</v>
       </c>
-      <c r="H266" t="inlineStr"/>
       <c r="I266" t="inlineStr">
         <is>
           <t>Active</t>
@@ -13777,7 +13666,6 @@
       <c r="F267" s="4" t="n">
         <v>45186</v>
       </c>
-      <c r="H267" t="inlineStr"/>
       <c r="I267" t="inlineStr">
         <is>
           <t>Active</t>
@@ -13822,7 +13710,6 @@
       <c r="F268" s="4" t="n">
         <v>45186</v>
       </c>
-      <c r="H268" t="inlineStr"/>
       <c r="I268" t="inlineStr">
         <is>
           <t>Active</t>
@@ -13867,7 +13754,6 @@
       <c r="F269" s="4" t="n">
         <v>45187</v>
       </c>
-      <c r="H269" t="inlineStr"/>
       <c r="I269" t="inlineStr">
         <is>
           <t>Active</t>
@@ -14016,7 +13902,6 @@
       <c r="F272" s="4" t="n">
         <v>45201</v>
       </c>
-      <c r="H272" t="inlineStr"/>
       <c r="I272" t="inlineStr">
         <is>
           <t>Active</t>
@@ -14113,7 +13998,6 @@
       <c r="F274" s="4" t="n">
         <v>45207</v>
       </c>
-      <c r="H274" t="inlineStr"/>
       <c r="I274" t="inlineStr">
         <is>
           <t>Active</t>
@@ -14158,7 +14042,6 @@
       <c r="F275" s="4" t="n">
         <v>45216</v>
       </c>
-      <c r="H275" t="inlineStr"/>
       <c r="I275" t="inlineStr">
         <is>
           <t>Active</t>
@@ -14203,7 +14086,6 @@
       <c r="F276" s="4" t="n">
         <v>45223</v>
       </c>
-      <c r="H276" t="inlineStr"/>
       <c r="I276" t="inlineStr">
         <is>
           <t>Active</t>
@@ -14248,7 +14130,6 @@
       <c r="F277" s="4" t="n">
         <v>45225</v>
       </c>
-      <c r="H277" t="inlineStr"/>
       <c r="I277" t="inlineStr">
         <is>
           <t>Active</t>
@@ -14293,7 +14174,6 @@
       <c r="F278" s="4" t="n">
         <v>45250</v>
       </c>
-      <c r="H278" t="inlineStr"/>
       <c r="I278" t="inlineStr">
         <is>
           <t>Active</t>
@@ -14390,7 +14270,6 @@
       <c r="F280" s="4" t="n">
         <v>45252</v>
       </c>
-      <c r="H280" t="inlineStr"/>
       <c r="I280" t="inlineStr">
         <is>
           <t>Active</t>
@@ -14435,7 +14314,6 @@
       <c r="F281" s="4" t="n">
         <v>45256</v>
       </c>
-      <c r="H281" t="inlineStr"/>
       <c r="I281" t="inlineStr">
         <is>
           <t>Active</t>
@@ -14480,7 +14358,6 @@
       <c r="F282" s="4" t="n">
         <v>45259</v>
       </c>
-      <c r="H282" t="inlineStr"/>
       <c r="I282" t="inlineStr">
         <is>
           <t>Active</t>
@@ -14577,7 +14454,6 @@
       <c r="F284" s="4" t="n">
         <v>45282</v>
       </c>
-      <c r="H284" t="inlineStr"/>
       <c r="I284" t="inlineStr">
         <is>
           <t>Active</t>
@@ -14778,7 +14654,6 @@
       <c r="F288" s="4" t="n">
         <v>45309</v>
       </c>
-      <c r="H288" t="inlineStr"/>
       <c r="I288" t="inlineStr">
         <is>
           <t>Active</t>
@@ -14823,7 +14698,6 @@
       <c r="F289" s="4" t="n">
         <v>45310</v>
       </c>
-      <c r="H289" t="inlineStr"/>
       <c r="I289" t="inlineStr">
         <is>
           <t>Active</t>
@@ -14868,7 +14742,6 @@
       <c r="F290" s="4" t="n">
         <v>45322</v>
       </c>
-      <c r="H290" t="inlineStr"/>
       <c r="I290" t="inlineStr">
         <is>
           <t>Active</t>
@@ -14913,7 +14786,6 @@
       <c r="F291" s="4" t="n">
         <v>45324</v>
       </c>
-      <c r="H291" t="inlineStr"/>
       <c r="I291" t="inlineStr">
         <is>
           <t>Active</t>
@@ -14958,7 +14830,6 @@
       <c r="F292" s="4" t="n">
         <v>45330</v>
       </c>
-      <c r="H292" t="inlineStr"/>
       <c r="I292" t="inlineStr">
         <is>
           <t>Active</t>
@@ -15003,7 +14874,6 @@
       <c r="F293" s="4" t="n">
         <v>45330</v>
       </c>
-      <c r="H293" t="inlineStr"/>
       <c r="I293" t="inlineStr">
         <is>
           <t>Active</t>
@@ -15152,7 +15022,6 @@
       <c r="F296" s="4" t="n">
         <v>45337</v>
       </c>
-      <c r="H296" t="inlineStr"/>
       <c r="I296" t="inlineStr">
         <is>
           <t>Active</t>
@@ -15197,7 +15066,6 @@
       <c r="F297" s="4" t="n">
         <v>45341</v>
       </c>
-      <c r="H297" t="inlineStr"/>
       <c r="I297" t="inlineStr">
         <is>
           <t>Active</t>
@@ -15294,7 +15162,6 @@
       <c r="F299" s="4" t="n">
         <v>45353</v>
       </c>
-      <c r="H299" t="inlineStr"/>
       <c r="I299" t="inlineStr">
         <is>
           <t>Active</t>
@@ -15339,7 +15206,6 @@
       <c r="F300" s="4" t="n">
         <v>45358</v>
       </c>
-      <c r="H300" t="inlineStr"/>
       <c r="I300" t="inlineStr">
         <is>
           <t>Active</t>
@@ -15436,7 +15302,6 @@
       <c r="F302" s="4" t="n">
         <v>45388</v>
       </c>
-      <c r="H302" t="inlineStr"/>
       <c r="I302" t="inlineStr">
         <is>
           <t>Active</t>
@@ -15481,7 +15346,6 @@
       <c r="F303" s="4" t="n">
         <v>45393</v>
       </c>
-      <c r="H303" t="inlineStr"/>
       <c r="I303" t="inlineStr">
         <is>
           <t>Active</t>
@@ -15526,7 +15390,6 @@
       <c r="F304" s="4" t="n">
         <v>45403</v>
       </c>
-      <c r="H304" t="inlineStr"/>
       <c r="I304" t="inlineStr">
         <is>
           <t>Active</t>
@@ -15623,7 +15486,6 @@
       <c r="F306" s="4" t="n">
         <v>45407</v>
       </c>
-      <c r="H306" t="inlineStr"/>
       <c r="I306" t="inlineStr">
         <is>
           <t>Active</t>
@@ -15668,7 +15530,6 @@
       <c r="F307" s="4" t="n">
         <v>45407</v>
       </c>
-      <c r="H307" t="inlineStr"/>
       <c r="I307" t="inlineStr">
         <is>
           <t>Active</t>
@@ -15713,7 +15574,6 @@
       <c r="F308" s="4" t="n">
         <v>45408</v>
       </c>
-      <c r="H308" t="inlineStr"/>
       <c r="I308" t="inlineStr">
         <is>
           <t>Active</t>
@@ -15758,7 +15618,6 @@
       <c r="F309" s="4" t="n">
         <v>45414</v>
       </c>
-      <c r="H309" t="inlineStr"/>
       <c r="I309" t="inlineStr">
         <is>
           <t>Active</t>
@@ -15803,7 +15662,6 @@
       <c r="F310" s="4" t="n">
         <v>45417</v>
       </c>
-      <c r="H310" t="inlineStr"/>
       <c r="I310" t="inlineStr">
         <is>
           <t>Active</t>
@@ -15848,7 +15706,6 @@
       <c r="F311" s="4" t="n">
         <v>45421</v>
       </c>
-      <c r="H311" t="inlineStr"/>
       <c r="I311" t="inlineStr">
         <is>
           <t>Active</t>
@@ -15945,7 +15802,6 @@
       <c r="F313" s="4" t="n">
         <v>45427</v>
       </c>
-      <c r="H313" t="inlineStr"/>
       <c r="I313" t="inlineStr">
         <is>
           <t>Active</t>
@@ -15990,7 +15846,6 @@
       <c r="F314" s="4" t="n">
         <v>45430</v>
       </c>
-      <c r="H314" t="inlineStr"/>
       <c r="I314" t="inlineStr">
         <is>
           <t>Active</t>
@@ -16139,7 +15994,6 @@
       <c r="F317" s="4" t="n">
         <v>45446</v>
       </c>
-      <c r="H317" t="inlineStr"/>
       <c r="I317" t="inlineStr">
         <is>
           <t>Active</t>
@@ -16184,7 +16038,6 @@
       <c r="F318" s="4" t="n">
         <v>45473</v>
       </c>
-      <c r="H318" t="inlineStr"/>
       <c r="I318" t="inlineStr">
         <is>
           <t>Active</t>
@@ -16281,7 +16134,6 @@
       <c r="F320" s="4" t="n">
         <v>45510</v>
       </c>
-      <c r="H320" t="inlineStr"/>
       <c r="I320" t="inlineStr">
         <is>
           <t>Active</t>
@@ -16326,7 +16178,6 @@
       <c r="F321" s="4" t="n">
         <v>45514</v>
       </c>
-      <c r="H321" t="inlineStr"/>
       <c r="I321" t="inlineStr">
         <is>
           <t>Active</t>
@@ -16371,7 +16222,6 @@
       <c r="F322" s="4" t="n">
         <v>45517</v>
       </c>
-      <c r="H322" t="inlineStr"/>
       <c r="I322" t="inlineStr">
         <is>
           <t>Active</t>
@@ -16468,7 +16318,6 @@
       <c r="F324" s="4" t="n">
         <v>45540</v>
       </c>
-      <c r="H324" t="inlineStr"/>
       <c r="I324" t="inlineStr">
         <is>
           <t>Active</t>
@@ -16513,7 +16362,6 @@
       <c r="F325" s="4" t="n">
         <v>45542</v>
       </c>
-      <c r="H325" t="inlineStr"/>
       <c r="I325" t="inlineStr">
         <is>
           <t>Active</t>
@@ -16610,7 +16458,6 @@
       <c r="F327" s="4" t="n">
         <v>45554</v>
       </c>
-      <c r="H327" t="inlineStr"/>
       <c r="I327" t="inlineStr">
         <is>
           <t>Active</t>
@@ -16707,7 +16554,6 @@
       <c r="F329" s="4" t="n">
         <v>45578</v>
       </c>
-      <c r="H329" t="inlineStr"/>
       <c r="I329" t="inlineStr">
         <is>
           <t>Active</t>
@@ -16752,7 +16598,6 @@
       <c r="F330" s="4" t="n">
         <v>45592</v>
       </c>
-      <c r="H330" t="inlineStr"/>
       <c r="I330" t="inlineStr">
         <is>
           <t>Active</t>
@@ -16797,7 +16642,6 @@
       <c r="F331" s="4" t="n">
         <v>45593</v>
       </c>
-      <c r="H331" t="inlineStr"/>
       <c r="I331" t="inlineStr">
         <is>
           <t>Active</t>
@@ -16894,7 +16738,6 @@
       <c r="F333" s="4" t="n">
         <v>45614</v>
       </c>
-      <c r="H333" t="inlineStr"/>
       <c r="I333" t="inlineStr">
         <is>
           <t>Active</t>
@@ -16939,7 +16782,6 @@
       <c r="F334" s="4" t="n">
         <v>45618</v>
       </c>
-      <c r="H334" t="inlineStr"/>
       <c r="I334" t="inlineStr">
         <is>
           <t>Active</t>
@@ -16984,7 +16826,6 @@
       <c r="F335" s="4" t="n">
         <v>45621</v>
       </c>
-      <c r="H335" t="inlineStr"/>
       <c r="I335" t="inlineStr">
         <is>
           <t>Active</t>
@@ -17029,7 +16870,6 @@
       <c r="F336" s="4" t="n">
         <v>45625</v>
       </c>
-      <c r="H336" t="inlineStr"/>
       <c r="I336" t="inlineStr">
         <is>
           <t>Active</t>
@@ -17074,7 +16914,6 @@
       <c r="F337" s="4" t="n">
         <v>45629</v>
       </c>
-      <c r="H337" t="inlineStr"/>
       <c r="I337" t="inlineStr">
         <is>
           <t>Active</t>
@@ -17223,7 +17062,6 @@
       <c r="F340" s="4" t="n">
         <v>45638</v>
       </c>
-      <c r="H340" t="inlineStr"/>
       <c r="I340" t="inlineStr">
         <is>
           <t>Active</t>
@@ -17268,7 +17106,6 @@
       <c r="F341" s="4" t="n">
         <v>45644</v>
       </c>
-      <c r="H341" t="inlineStr"/>
       <c r="I341" t="inlineStr">
         <is>
           <t>Active</t>
@@ -17417,7 +17254,6 @@
       <c r="F344" s="4" t="n">
         <v>45665</v>
       </c>
-      <c r="H344" t="inlineStr"/>
       <c r="I344" t="inlineStr">
         <is>
           <t>Active</t>
@@ -17514,7 +17350,6 @@
       <c r="F346" s="4" t="n">
         <v>45674</v>
       </c>
-      <c r="H346" t="inlineStr"/>
       <c r="I346" t="inlineStr">
         <is>
           <t>Active</t>
@@ -17559,7 +17394,6 @@
       <c r="F347" s="4" t="n">
         <v>45680</v>
       </c>
-      <c r="H347" t="inlineStr"/>
       <c r="I347" t="inlineStr">
         <is>
           <t>Active</t>
@@ -17604,7 +17438,6 @@
       <c r="F348" s="4" t="n">
         <v>45687</v>
       </c>
-      <c r="H348" t="inlineStr"/>
       <c r="I348" t="inlineStr">
         <is>
           <t>Active</t>
@@ -17753,7 +17586,6 @@
       <c r="F351" s="4" t="n">
         <v>45705</v>
       </c>
-      <c r="H351" t="inlineStr"/>
       <c r="I351" t="inlineStr">
         <is>
           <t>Active</t>
@@ -17850,7 +17682,6 @@
       <c r="F353" s="4" t="n">
         <v>45709</v>
       </c>
-      <c r="H353" t="inlineStr"/>
       <c r="I353" t="inlineStr">
         <is>
           <t>Active</t>
@@ -17895,7 +17726,6 @@
       <c r="F354" s="4" t="n">
         <v>45723</v>
       </c>
-      <c r="H354" t="inlineStr"/>
       <c r="I354" t="inlineStr">
         <is>
           <t>Active</t>
@@ -17940,7 +17770,6 @@
       <c r="F355" s="4" t="n">
         <v>45727</v>
       </c>
-      <c r="H355" t="inlineStr"/>
       <c r="I355" t="inlineStr">
         <is>
           <t>Active</t>
@@ -17985,7 +17814,6 @@
       <c r="F356" s="4" t="n">
         <v>45729</v>
       </c>
-      <c r="H356" t="inlineStr"/>
       <c r="I356" t="inlineStr">
         <is>
           <t>Active</t>
@@ -18030,7 +17858,6 @@
       <c r="F357" s="4" t="n">
         <v>45730</v>
       </c>
-      <c r="H357" t="inlineStr"/>
       <c r="I357" t="inlineStr">
         <is>
           <t>Active</t>
@@ -18075,7 +17902,6 @@
       <c r="F358" s="4" t="n">
         <v>45731</v>
       </c>
-      <c r="H358" t="inlineStr"/>
       <c r="I358" t="inlineStr">
         <is>
           <t>Active</t>
@@ -18120,7 +17946,6 @@
       <c r="F359" s="4" t="n">
         <v>45733</v>
       </c>
-      <c r="H359" t="inlineStr"/>
       <c r="I359" t="inlineStr">
         <is>
           <t>Active</t>
@@ -18165,7 +17990,6 @@
       <c r="F360" s="4" t="n">
         <v>45745</v>
       </c>
-      <c r="H360" t="inlineStr"/>
       <c r="I360" t="inlineStr">
         <is>
           <t>Active</t>
@@ -18210,7 +18034,6 @@
       <c r="F361" s="4" t="n">
         <v>45746</v>
       </c>
-      <c r="H361" t="inlineStr"/>
       <c r="I361" t="inlineStr">
         <is>
           <t>Active</t>
@@ -18255,7 +18078,6 @@
       <c r="F362" s="4" t="n">
         <v>45766</v>
       </c>
-      <c r="H362" t="inlineStr"/>
       <c r="I362" t="inlineStr">
         <is>
           <t>Active</t>
@@ -18352,7 +18174,6 @@
       <c r="F364" s="4" t="n">
         <v>45792</v>
       </c>
-      <c r="H364" t="inlineStr"/>
       <c r="I364" t="inlineStr">
         <is>
           <t>Active</t>
@@ -18397,7 +18218,6 @@
       <c r="F365" s="4" t="n">
         <v>45804</v>
       </c>
-      <c r="H365" t="inlineStr"/>
       <c r="I365" t="inlineStr">
         <is>
           <t>Active</t>
@@ -18442,7 +18262,6 @@
       <c r="F366" s="4" t="n">
         <v>45864</v>
       </c>
-      <c r="H366" t="inlineStr"/>
       <c r="I366" t="inlineStr">
         <is>
           <t>Active</t>
@@ -18487,7 +18306,6 @@
       <c r="F367" s="4" t="n">
         <v>45869</v>
       </c>
-      <c r="H367" t="inlineStr"/>
       <c r="I367" t="inlineStr">
         <is>
           <t>Active</t>
@@ -18532,7 +18350,6 @@
       <c r="F368" s="4" t="n">
         <v>45873</v>
       </c>
-      <c r="H368" t="inlineStr"/>
       <c r="I368" t="inlineStr">
         <is>
           <t>Active</t>
@@ -18577,7 +18394,6 @@
       <c r="F369" s="4" t="n">
         <v>45879</v>
       </c>
-      <c r="H369" t="inlineStr"/>
       <c r="I369" t="inlineStr">
         <is>
           <t>Active</t>
@@ -18622,7 +18438,6 @@
       <c r="F370" s="4" t="n">
         <v>45884</v>
       </c>
-      <c r="H370" t="inlineStr"/>
       <c r="I370" t="inlineStr">
         <is>
           <t>Active</t>
@@ -18719,7 +18534,6 @@
       <c r="F372" s="4" t="n">
         <v>45887</v>
       </c>
-      <c r="H372" t="inlineStr"/>
       <c r="I372" t="inlineStr">
         <is>
           <t>Active</t>
@@ -18764,7 +18578,6 @@
       <c r="F373" s="4" t="n">
         <v>45888</v>
       </c>
-      <c r="H373" t="inlineStr"/>
       <c r="I373" t="inlineStr">
         <is>
           <t>Active</t>
@@ -18809,7 +18622,6 @@
       <c r="F374" s="4" t="n">
         <v>45889</v>
       </c>
-      <c r="H374" t="inlineStr"/>
       <c r="I374" t="inlineStr">
         <is>
           <t>Active</t>
@@ -18854,7 +18666,6 @@
       <c r="F375" s="4" t="n">
         <v>45891</v>
       </c>
-      <c r="H375" t="inlineStr"/>
       <c r="I375" t="inlineStr">
         <is>
           <t>Active</t>
@@ -18899,7 +18710,6 @@
       <c r="F376" s="4" t="n">
         <v>45901</v>
       </c>
-      <c r="H376" t="inlineStr"/>
       <c r="I376" t="inlineStr">
         <is>
           <t>Active</t>
@@ -18944,7 +18754,6 @@
       <c r="F377" s="4" t="n">
         <v>45903</v>
       </c>
-      <c r="H377" t="inlineStr"/>
       <c r="I377" t="inlineStr">
         <is>
           <t>Active</t>
@@ -18989,7 +18798,6 @@
       <c r="F378" s="4" t="n">
         <v>45905</v>
       </c>
-      <c r="H378" t="inlineStr"/>
       <c r="I378" t="inlineStr">
         <is>
           <t>Active</t>
@@ -19034,7 +18842,6 @@
       <c r="F379" s="4" t="n">
         <v>45905</v>
       </c>
-      <c r="H379" t="inlineStr"/>
       <c r="I379" t="inlineStr">
         <is>
           <t>Active</t>
@@ -19079,7 +18886,6 @@
       <c r="F380" s="4" t="n">
         <v>45913</v>
       </c>
-      <c r="H380" t="inlineStr"/>
       <c r="I380" t="inlineStr">
         <is>
           <t>Active</t>
@@ -19124,7 +18930,6 @@
       <c r="F381" s="4" t="n">
         <v>45917</v>
       </c>
-      <c r="H381" t="inlineStr"/>
       <c r="I381" t="inlineStr">
         <is>
           <t>Active</t>
@@ -19221,7 +19026,6 @@
       <c r="F383" s="4" t="n">
         <v>45922</v>
       </c>
-      <c r="H383" t="inlineStr"/>
       <c r="I383" t="inlineStr">
         <is>
           <t>Active</t>
@@ -19266,7 +19070,6 @@
       <c r="F384" s="4" t="n">
         <v>45942</v>
       </c>
-      <c r="H384" t="inlineStr"/>
       <c r="I384" t="inlineStr">
         <is>
           <t>Active</t>
@@ -19311,7 +19114,6 @@
       <c r="F385" s="4" t="n">
         <v>45944</v>
       </c>
-      <c r="H385" t="inlineStr"/>
       <c r="I385" t="inlineStr">
         <is>
           <t>Active</t>
@@ -19356,7 +19158,6 @@
       <c r="F386" s="4" t="n">
         <v>45955</v>
       </c>
-      <c r="H386" t="inlineStr"/>
       <c r="I386" t="inlineStr">
         <is>
           <t>Active</t>
@@ -19401,7 +19202,6 @@
       <c r="F387" s="4" t="n">
         <v>45962</v>
       </c>
-      <c r="H387" t="inlineStr"/>
       <c r="I387" t="inlineStr">
         <is>
           <t>Active</t>
@@ -19446,7 +19246,6 @@
       <c r="F388" s="4" t="n">
         <v>45963</v>
       </c>
-      <c r="H388" t="inlineStr"/>
       <c r="I388" t="inlineStr">
         <is>
           <t>Active</t>
@@ -19491,7 +19290,6 @@
       <c r="F389" s="4" t="n">
         <v>45968</v>
       </c>
-      <c r="H389" t="inlineStr"/>
       <c r="I389" t="inlineStr">
         <is>
           <t>Active</t>
@@ -19536,7 +19334,6 @@
       <c r="F390" s="4" t="n">
         <v>45974</v>
       </c>
-      <c r="H390" t="inlineStr"/>
       <c r="I390" t="inlineStr">
         <is>
           <t>Active</t>
@@ -19581,7 +19378,6 @@
       <c r="F391" s="4" t="n">
         <v>45982</v>
       </c>
-      <c r="H391" t="inlineStr"/>
       <c r="I391" t="inlineStr">
         <is>
           <t>Active</t>
@@ -19626,7 +19422,6 @@
       <c r="F392" s="4" t="n">
         <v>45987</v>
       </c>
-      <c r="H392" t="inlineStr"/>
       <c r="I392" t="inlineStr">
         <is>
           <t>Active</t>
@@ -19671,7 +19466,6 @@
       <c r="F393" s="4" t="n">
         <v>46006</v>
       </c>
-      <c r="H393" t="inlineStr"/>
       <c r="I393" t="inlineStr">
         <is>
           <t>Active</t>
@@ -19716,7 +19510,6 @@
       <c r="F394" s="4" t="n">
         <v>46010</v>
       </c>
-      <c r="H394" t="inlineStr"/>
       <c r="I394" t="inlineStr">
         <is>
           <t>Active</t>
@@ -19761,7 +19554,6 @@
       <c r="F395" s="4" t="n">
         <v>46014</v>
       </c>
-      <c r="H395" t="inlineStr"/>
       <c r="I395" t="inlineStr">
         <is>
           <t>Active</t>
@@ -19806,7 +19598,6 @@
       <c r="F396" s="4" t="n">
         <v>46024</v>
       </c>
-      <c r="H396" t="inlineStr"/>
       <c r="I396" t="inlineStr">
         <is>
           <t>Active</t>
@@ -19851,7 +19642,6 @@
       <c r="F397" s="4" t="n">
         <v>46027</v>
       </c>
-      <c r="H397" t="inlineStr"/>
       <c r="I397" t="inlineStr">
         <is>
           <t>Active</t>
@@ -19896,7 +19686,6 @@
       <c r="F398" s="4" t="n">
         <v>46047</v>
       </c>
-      <c r="H398" t="inlineStr"/>
       <c r="I398" t="inlineStr">
         <is>
           <t>Active</t>
@@ -19941,7 +19730,6 @@
       <c r="F399" s="4" t="n">
         <v>46061</v>
       </c>
-      <c r="H399" t="inlineStr"/>
       <c r="I399" t="inlineStr">
         <is>
           <t>Active</t>
@@ -19986,7 +19774,6 @@
       <c r="F400" s="4" t="n">
         <v>46062</v>
       </c>
-      <c r="H400" t="inlineStr"/>
       <c r="I400" t="inlineStr">
         <is>
           <t>Active</t>
@@ -20031,7 +19818,6 @@
       <c r="F401" s="4" t="n">
         <v>46066</v>
       </c>
-      <c r="H401" t="inlineStr"/>
       <c r="I401" t="inlineStr">
         <is>
           <t>Active</t>
@@ -20076,7 +19862,6 @@
       <c r="F402" s="4" t="n">
         <v>46071</v>
       </c>
-      <c r="H402" t="inlineStr"/>
       <c r="I402" t="inlineStr">
         <is>
           <t>Active</t>
@@ -20121,7 +19906,6 @@
       <c r="F403" s="4" t="n">
         <v>46073</v>
       </c>
-      <c r="H403" t="inlineStr"/>
       <c r="I403" t="inlineStr">
         <is>
           <t>Active</t>
@@ -20166,7 +19950,6 @@
       <c r="F404" s="4" t="n">
         <v>46077</v>
       </c>
-      <c r="H404" t="inlineStr"/>
       <c r="I404" t="inlineStr">
         <is>
           <t>Active</t>
@@ -20211,7 +19994,6 @@
       <c r="F405" s="4" t="n">
         <v>46084</v>
       </c>
-      <c r="H405" t="inlineStr"/>
       <c r="I405" t="inlineStr">
         <is>
           <t>Active</t>
@@ -20256,7 +20038,6 @@
       <c r="F406" s="4" t="n">
         <v>46106</v>
       </c>
-      <c r="H406" t="inlineStr"/>
       <c r="I406" t="inlineStr">
         <is>
           <t>Active</t>
@@ -20301,7 +20082,6 @@
       <c r="F407" s="4" t="n">
         <v>46119</v>
       </c>
-      <c r="H407" t="inlineStr"/>
       <c r="I407" t="inlineStr">
         <is>
           <t>Active</t>
@@ -20346,7 +20126,6 @@
       <c r="F408" s="4" t="n">
         <v>46129</v>
       </c>
-      <c r="H408" t="inlineStr"/>
       <c r="I408" t="inlineStr">
         <is>
           <t>Active</t>
@@ -20391,7 +20170,6 @@
       <c r="F409" s="4" t="n">
         <v>46129</v>
       </c>
-      <c r="H409" t="inlineStr"/>
       <c r="I409" t="inlineStr">
         <is>
           <t>Active</t>
@@ -20436,7 +20214,6 @@
       <c r="F410" s="4" t="n">
         <v>46130</v>
       </c>
-      <c r="H410" t="inlineStr"/>
       <c r="I410" t="inlineStr">
         <is>
           <t>Active</t>
@@ -20481,7 +20258,6 @@
       <c r="F411" s="4" t="n">
         <v>46135</v>
       </c>
-      <c r="H411" t="inlineStr"/>
       <c r="I411" t="inlineStr">
         <is>
           <t>Active</t>
@@ -20526,7 +20302,6 @@
       <c r="F412" s="4" t="n">
         <v>46137</v>
       </c>
-      <c r="H412" t="inlineStr"/>
       <c r="I412" t="inlineStr">
         <is>
           <t>Active</t>
@@ -20571,7 +20346,6 @@
       <c r="F413" s="4" t="n">
         <v>46138</v>
       </c>
-      <c r="H413" t="inlineStr"/>
       <c r="I413" t="inlineStr">
         <is>
           <t>Active</t>
@@ -20616,7 +20390,6 @@
       <c r="F414" s="4" t="n">
         <v>46138</v>
       </c>
-      <c r="H414" t="inlineStr"/>
       <c r="I414" t="inlineStr">
         <is>
           <t>Active</t>
@@ -20661,7 +20434,6 @@
       <c r="F415" s="4" t="n">
         <v>46141</v>
       </c>
-      <c r="H415" t="inlineStr"/>
       <c r="I415" t="inlineStr">
         <is>
           <t>Active</t>
@@ -20706,7 +20478,6 @@
       <c r="F416" s="4" t="n">
         <v>46141</v>
       </c>
-      <c r="H416" t="inlineStr"/>
       <c r="I416" t="inlineStr">
         <is>
           <t>Active</t>
@@ -20751,7 +20522,6 @@
       <c r="F417" s="4" t="n">
         <v>46146</v>
       </c>
-      <c r="H417" t="inlineStr"/>
       <c r="I417" t="inlineStr">
         <is>
           <t>Active</t>
@@ -20796,7 +20566,6 @@
       <c r="F418" s="4" t="n">
         <v>46146</v>
       </c>
-      <c r="H418" t="inlineStr"/>
       <c r="I418" t="inlineStr">
         <is>
           <t>Active</t>
@@ -20841,7 +20610,6 @@
       <c r="F419" s="4" t="n">
         <v>46146</v>
       </c>
-      <c r="H419" t="inlineStr"/>
       <c r="I419" t="inlineStr">
         <is>
           <t>Active</t>
@@ -20886,7 +20654,6 @@
       <c r="F420" s="4" t="n">
         <v>46153</v>
       </c>
-      <c r="H420" t="inlineStr"/>
       <c r="I420" t="inlineStr">
         <is>
           <t>Active</t>
@@ -20931,7 +20698,6 @@
       <c r="F421" s="4" t="n">
         <v>46155</v>
       </c>
-      <c r="H421" t="inlineStr"/>
       <c r="I421" t="inlineStr">
         <is>
           <t>Active</t>
@@ -21074,7 +20840,6 @@
       <c r="F2" s="4" t="n">
         <v>46216</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Active</t>
@@ -21116,7 +20881,6 @@
       <c r="F3" s="4" t="n">
         <v>46216</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Active</t>
@@ -21158,7 +20922,6 @@
       <c r="F4" s="4" t="n">
         <v>46204</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Active</t>
@@ -21200,7 +20963,6 @@
       <c r="F5" s="4" t="n">
         <v>46204</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Active</t>
@@ -21242,7 +21004,6 @@
       <c r="F6" s="4" t="n">
         <v>46216</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Active</t>
@@ -21284,7 +21045,6 @@
       <c r="F7" s="4" t="n">
         <v>46223</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Active</t>
@@ -21326,7 +21086,6 @@
       <c r="F8" s="4" t="n">
         <v>46209</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Active</t>
@@ -21368,7 +21127,6 @@
       <c r="F9" s="4" t="n">
         <v>46204</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Active</t>
@@ -21405,12 +21163,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
@@ -21448,7 +21206,322 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>2 · A</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>Add three columns to tblEmployees:
+1) Active_Start = TRUE if Hire_Date &lt;= 2025-07-01 and (Exit_Date is blank or Exit_Date &gt; 2025-07-01).
+2) Exit_In_Period = TRUE if Exit_Date is between 2025-07-01 and 2026-06-30 inclusive.
+3) Tenure_Years = years from Hire_Date to Exit_Date, or to 2026-06-30 if Exit_Date is blank, 1 decimal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>2 · B</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Explain the Active_Start formula, and show one employee who exited before 2025-07-01 with Hire_Date, Exit_Date and Active_Start.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>3 · C</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Create a sheet named Checks. Put these labels in column A and formulas in column B exactly as written, then tell me each result. Build the Attrition rate formula from the cells above it:
+Active headcount     =COUNTIFS(tblEmployees[Status],"Active")
+Headcount 2025-07-01 =COUNTIFS(tblEmployees[Active_Start],TRUE)
+Exits in period      =COUNTIFS(tblEmployees[Exit_In_Period],TRUE)
+Voluntary exits      =COUNTIFS(tblEmployees[Exit_In_Period],TRUE,tblEmployees[Exit_Type],"Voluntary") Attrition rate       = Exits in period / ((Headcount 2025-07-01 + Active headcount) / 2)
+Hires in period      =COUNTIFS(tblEmployees[Hire_Date],"&gt;="&amp;DATE(2025,7,1),tblEmployees[Hire_Date],"&lt;="&amp;DATE(2026,6,30))</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>4 · D</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Plan an HR workforce dashboard on the HR_Dashboard sheet from tblEmployees for the HR Director. KPI cards (formulas): Active headcount, Exits (last 12 months), Attrition rate, Voluntary attrition rate, Avg tenure of active staff (years), Hires (last 12 months). Use the definitions on About_This_Data.
+Charts: active headcount by Department (bar, sorted); attrition rate by Department (bar); hires vs exits by quarter for the last 12 months (clustered column); active headcount by Location (bar).
+Slicers: Location and Job_Level, connected to all PivotTables. Title and "Data as at 2026-06-30". Do not show Employee_ID, salary or individual records on the dashboard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>5 · E</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Chat</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Compare each KPI card on HR_Dashboard with the Checks sheet and tell me which, if any, do not match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>5 · F</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Chat</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>The attrition rate must use average headcount = (Active_Start count + active count) / 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>5 · G</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Chat</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Which combinations of Location, Job_Level and Department contain fewer than 5 active employees?</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>6 · H</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Copy the 8 data rows in New_Joiners_Jul2026!A2:L9 to the first empty rows directly below tblEmployees so the table expands. Then refresh all PivotTables in the workbook and tell me the new Active headcount and the number of rows in tblEmployees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>7 · I</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Chat</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Review HR_Dashboard before I share it with the leadership team. Does any element expose individual employee data or a group smaller than 5? Is each KPI labelled with its period and definition?</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>7 · J</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Prompt_Log already lists every prompt in this lab. For each one I ran, fill in What Copilot did and How I verified, and set Decision to Keep. I will tell you any row to change to Revise or Undo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Extra 1</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Add Active_Start = TRUE if Hire_Date &lt;= 2025-07-01 and Exit_Date is blank or after 2025-07-01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Extra 2</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Add Tenure_Years from Hire_Date to Exit_Date, or to 2026-06-30 if Exit_Date is blank, rounded to 1 decimal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Extra 3</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Plan an HR workforce dashboard with KPI cards for active headcount, exits, attrition rate, voluntary attrition, average tenure and hires.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>Extra 4</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Create a bar chart of 12-month attrition rate by Department, sorted highest first, with data labels as percentages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Extra 5</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Add slicers for Location and Job_Level and connect them to every PivotTable on the dashboard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Extra 6</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>I added rows to tblEmployees. Refresh all PivotTables and tell me which KPI values changed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Extra 7</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Which slicer combinations show a group of fewer than 5 employees? Suggest how to suppress them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Extra 8</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Explain how the Attrition rate card is calculated, step by step.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
